--- a/output/pdf_financials_xlsx/BMM.xlsx
+++ b/output/pdf_financials_xlsx/BMM.xlsx
@@ -1278,7 +1278,7 @@
         <v>0.029061</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.201603</v>
+        <v>-0.201603</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-0.140726</v>
@@ -1566,7 +1566,7 @@
         <v>0.029061</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.201603</v>
+        <v>-0.201603</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-0.140726</v>
@@ -1735,7 +1735,7 @@
         <v>0.029061</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.201603</v>
+        <v>-0.201603</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-0.140726</v>
@@ -2001,7 +2001,7 @@
         <v>0.029061</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.201603</v>
+        <v>-0.201603</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-0.140726</v>
@@ -2115,7 +2115,7 @@
         <v>0.032015</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.203051</v>
+        <v>-0.200155</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-0.139713</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -5774,19 +5774,19 @@
         <v>1.215374</v>
       </c>
       <c r="C92" s="3" t="n">
+        <v>1.215374</v>
+      </c>
+      <c r="D92" s="3" t="n">
         <v>1.653719</v>
       </c>
-      <c r="D92" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.886312</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.886312</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.886312</v>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
@@ -5794,31 +5794,31 @@
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.903761</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.945512</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.945512</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.945512</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.921541</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.970937</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.015072</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.310967</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.529411</v>
       </c>
     </row>
     <row r="93">
@@ -7216,13 +7216,13 @@
         <v>0.406793</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.236556</v>
+        <v>-0.102174</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.221192</v>
+        <v>-2.002793</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0.212279</v>
+        <v>-5.352836</v>
       </c>
     </row>
     <row r="119">
@@ -9580,7 +9580,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10860,7 +10864,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -11232,7 +11240,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -14752,7 +14764,11 @@
           <t>Reserves 1,861,312</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -17586,7 +17602,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -31433,7 +31453,7 @@
         </is>
       </c>
       <c r="P247" s="5" t="n">
-        <v>0.201603</v>
+        <v>-0.201603</v>
       </c>
       <c r="Q247" s="5" t="n">
         <v>-0.140726</v>

--- a/output/pdf_financials_xlsx/BMM.xlsx
+++ b/output/pdf_financials_xlsx/BMM.xlsx
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000954</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>2.9e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000127</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000104</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1966,16 +1966,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.316363</v>
+        <v>-0.317317</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.441214</v>
+        <v>-1.441243</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.072135</v>
+        <v>-1.072262</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.313079</v>
+        <v>-1.313183</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.384212</v>
@@ -2080,16 +2080,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.316363</v>
+        <v>-0.317317</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.441214</v>
+        <v>-1.441243</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.072135</v>
+        <v>-1.072262</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.313079</v>
+        <v>-1.313183</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.384212</v>
@@ -2375,22 +2375,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.644257</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.644257</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.009520000000000001</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>8.1e-05</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
@@ -2398,31 +2398,31 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.050112</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.304074</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.260244</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.148924</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.005274</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.124698</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.0418</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>3.399917</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.32234</v>
       </c>
     </row>
     <row r="35">
@@ -2489,22 +2489,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.0115</v>
+        <v>0.655757</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.0115</v>
+        <v>0.655757</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.0115</v>
+        <v>0.02102</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>8.1e-05</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
@@ -2512,31 +2512,31 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.050112</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.304074</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.260244</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.148924</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.005274</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.124698</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.0418</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>3.399917</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.32234</v>
       </c>
     </row>
     <row r="37">
@@ -3173,19 +3173,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.644257</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.644257</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.051035</v>
+        <v>0.041515</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>8.1e-05</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -3196,31 +3196,31 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.090626</v>
+        <v>0.040514</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.341512</v>
+        <v>0.037438</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.283908</v>
+        <v>0.023664</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.151216</v>
+        <v>0.002292</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.00923</v>
+        <v>0.003956</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.127695</v>
+        <v>0.002997</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.044451</v>
+        <v>0.002651</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>3.412731</v>
+        <v>0.012814</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.344235</v>
+        <v>0.021895</v>
       </c>
     </row>
     <row r="49">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
@@ -37868,7 +37868,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -39896,7 +39896,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -41456,7 +41456,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E352" s="5" t="n">
